--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,289 +233,289 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ABAD</t>
+  </si>
+  <si>
     <t>AYOHUA</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CAHUICH</t>
+  </si>
+  <si>
+    <t>CALDERON</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
     <t>LEYVA</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PUGA</t>
+  </si>
+  <si>
+    <t>QUINTANA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>DORANTES</t>
+  </si>
+  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
+    <t>ESPEJO</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>VELASQUEZ</t>
   </si>
   <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>MARIA CHRISTINA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>MELANY SHARENY</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
+  </si>
+  <si>
+    <t>LESLIE PAOLA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
     <t>CAROLINA</t>
   </si>
   <si>
+    <t>ARANZA MARLENE</t>
+  </si>
+  <si>
+    <t>MARIA CECILIA</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>ESTRELLA</t>
   </si>
   <si>
-    <t>DANA PAOLA</t>
+    <t>MARIA ELISA</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>LUZ YAMILET</t>
+  </si>
+  <si>
+    <t>ROSA</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>HILEN ALELI</t>
+  </si>
+  <si>
+    <t>SOFIA</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>ULISES</t>
+  </si>
+  <si>
+    <t>MAYRIN FERNANDA</t>
+  </si>
+  <si>
+    <t>ARLETT ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ALEXANDRA</t>
   </si>
   <si>
     <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CAHUICH</t>
-  </si>
-  <si>
-    <t>CALDERON</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PUGA</t>
-  </si>
-  <si>
-    <t>QUINTANA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>ESPEJO</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIA CHRISTINA</t>
-  </si>
-  <si>
-    <t>MELANY SHARENY</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>LESLIE PAOLA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ARANZA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>MARIA ELISA</t>
-  </si>
-  <si>
-    <t>CARLOS EDUARDO</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>LUZ YAMILET</t>
-  </si>
-  <si>
-    <t>ROSA</t>
-  </si>
-  <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
-    <t>HILEN ALELI</t>
-  </si>
-  <si>
-    <t>SOFIA</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>ULISES</t>
-  </si>
-  <si>
-    <t>MAYRIN FERNANDA</t>
-  </si>
-  <si>
-    <t>ARLETT ALEJANDRA</t>
-  </si>
-  <si>
-    <t>ALEXANDRA</t>
   </si>
   <si>
     <t>DORIS ALINE</t>
@@ -1034,19 +1034,19 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1076,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1105,16 +1105,16 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1123,7 +1123,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1159,7 +1159,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1188,19 +1188,19 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1224,10 +1224,10 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1265,19 +1265,19 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1301,10 +1301,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1342,19 +1342,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1384,13 +1384,13 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1419,10 +1419,10 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1431,7 +1431,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1458,7 +1458,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1467,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1496,19 +1496,19 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1532,13 +1532,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1573,19 +1573,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1609,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1650,19 +1650,19 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1689,10 +1689,10 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1727,19 +1727,19 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1769,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1804,19 +1804,19 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1881,19 +1881,19 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1923,7 +1923,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1958,19 +1958,19 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1994,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2006,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2035,19 +2035,19 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2112,19 +2112,19 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2183,25 +2183,25 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2228,7 +2228,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2237,7 +2237,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2266,19 +2266,19 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2343,19 +2343,19 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2379,13 +2379,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2414,25 +2414,25 @@
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2462,13 +2462,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2491,25 +2491,25 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2539,13 +2539,13 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2574,19 +2574,19 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2613,10 +2613,10 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2651,19 +2651,19 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2728,19 +2728,19 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2764,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2805,10 +2805,10 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2817,7 +2817,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2844,7 +2844,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2853,7 +2853,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2882,19 +2882,19 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2918,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2953,25 +2953,25 @@
         <v>5</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3007,7 +3007,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3036,19 +3036,19 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3113,19 +3113,19 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3149,7 +3149,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3190,19 +3190,19 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3226,7 +3226,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3267,19 +3267,19 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3344,19 +3344,19 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3421,19 +3421,19 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3457,7 +3457,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3498,19 +3498,19 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3534,7 +3534,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>10</v>
@@ -3546,7 +3546,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3569,16 +3569,16 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3587,7 +3587,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3614,7 +3614,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3623,7 +3623,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3652,19 +3652,19 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3729,19 +3729,19 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3765,19 +3765,19 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>8</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3806,19 +3806,19 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3854,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3883,19 +3883,19 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3925,13 +3925,13 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>9</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -3960,19 +3960,19 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -3999,7 +3999,7 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>5</v>
@@ -4037,19 +4037,19 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4079,13 +4079,13 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
       </c>
       <c r="X43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y43">
         <v>7</v>
@@ -4153,16 +4153,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="G2">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -4220,22 +4220,22 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>85</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4281,19 +4281,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4341,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4366,126 +4366,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920333</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920065</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920334</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920067</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920071</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920079</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4521,115 +4401,115 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920333</v>
+        <v>22330051920052</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920065</v>
+        <v>22330051920333</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920334</v>
+        <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920067</v>
+        <v>22330051920054</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920071</v>
+        <v>22330051920055</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920079</v>
+        <v>22330051920056</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920052</v>
+        <v>22330051920208</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>138</v>
@@ -4640,13 +4520,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920053</v>
+        <v>22330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>139</v>
@@ -4657,13 +4537,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920054</v>
+        <v>22330051920058</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>140</v>
@@ -4674,13 +4554,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920055</v>
+        <v>22330051920059</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>141</v>
@@ -4691,16 +4571,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920056</v>
+        <v>22330051920061</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4708,16 +4588,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920208</v>
+        <v>22330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4725,16 +4605,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920057</v>
+        <v>22330051920060</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4742,16 +4622,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920058</v>
+        <v>22330051920063</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4759,16 +4639,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920059</v>
+        <v>22330051920064</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4776,16 +4656,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920061</v>
+        <v>22330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4793,16 +4673,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920062</v>
+        <v>22330051920066</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4810,16 +4690,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920060</v>
+        <v>22330051920316</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4827,16 +4707,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920063</v>
+        <v>22330051920334</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4844,16 +4724,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920064</v>
+        <v>22330051920067</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4861,16 +4741,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920066</v>
+        <v>22330051920335</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4878,16 +4758,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920316</v>
+        <v>22330051920380</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4895,16 +4775,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920335</v>
+        <v>22330051920068</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4912,16 +4792,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920380</v>
+        <v>22330051920069</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4929,16 +4809,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920068</v>
+        <v>22330051920070</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4946,16 +4826,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920069</v>
+        <v>22330051920071</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4963,13 +4843,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920070</v>
+        <v>22330051920072</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>157</v>
@@ -4980,13 +4860,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920072</v>
+        <v>22330051920073</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>158</v>
@@ -4997,13 +4877,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920073</v>
+        <v>22330051920074</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
         <v>159</v>
@@ -5014,13 +4894,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920074</v>
+        <v>22330051920075</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
         <v>160</v>
@@ -5031,13 +4911,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920075</v>
+        <v>22330051920076</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
         <v>161</v>
@@ -5048,13 +4928,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920076</v>
+        <v>22330051920077</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
         <v>162</v>
@@ -5065,13 +4945,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920077</v>
+        <v>22330051920078</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>163</v>
@@ -5082,13 +4962,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920078</v>
+        <v>22330051920081</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
         <v>164</v>
@@ -5099,13 +4979,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920081</v>
+        <v>22330051920079</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>165</v>
@@ -5119,10 +4999,10 @@
         <v>22330051920080</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
         <v>166</v>
@@ -5136,10 +5016,10 @@
         <v>22330051920082</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
         <v>167</v>
@@ -5153,10 +5033,10 @@
         <v>22330051920083</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
         <v>168</v>
@@ -5170,10 +5050,10 @@
         <v>22330051920336</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
         <v>169</v>
@@ -5187,10 +5067,10 @@
         <v>22330051920084</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
         <v>170</v>
@@ -5206,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5241,13 +5121,13 @@
         <v>22330051920065</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5264,13 +5144,13 @@
         <v>22330051920065</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5279,44 +5159,44 @@
         <v>63</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920067</v>
+        <v>22330051920084</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920067</v>
+        <v>22330051920084</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5330,22 +5210,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920068</v>
+        <v>22330051920053</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5353,22 +5233,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>22330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5376,16 +5256,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920069</v>
+        <v>22330051920059</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5399,22 +5279,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920069</v>
+        <v>22330051920061</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5422,22 +5302,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920084</v>
+        <v>22330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5445,22 +5325,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920084</v>
+        <v>22330051920064</v>
       </c>
       <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
         <v>114</v>
       </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5468,16 +5348,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920053</v>
+        <v>22330051920334</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5491,22 +5371,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920054</v>
+        <v>22330051920067</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5514,139 +5394,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920062</v>
+        <v>22330051920079</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920064</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920066</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920334</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920079</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920336</v>
-      </c>
-      <c r="B19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -1043,13 +1043,13 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1117,16 +1117,16 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1197,13 +1197,13 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1239,7 +1239,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1274,13 +1274,13 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1310,13 +1310,13 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1351,13 +1351,13 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1425,16 +1425,16 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1505,13 +1505,13 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1582,13 +1582,13 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1624,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1659,13 +1659,13 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1695,7 +1695,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1736,13 +1736,13 @@
         <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1778,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1813,13 +1813,13 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1890,13 +1890,13 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1932,7 +1932,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1967,13 +1967,13 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2009,7 +2009,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2044,13 +2044,13 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2080,13 +2080,13 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2121,13 +2121,13 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2157,13 +2157,13 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2198,13 +2198,13 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2234,13 +2234,13 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2275,13 +2275,13 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2311,7 +2311,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2352,13 +2352,13 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2388,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2429,13 +2429,13 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2465,7 +2465,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2506,13 +2506,13 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2583,13 +2583,13 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2660,13 +2660,13 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2737,13 +2737,13 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2773,13 +2773,13 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2811,16 +2811,16 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2891,13 +2891,13 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2927,13 +2927,13 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2968,13 +2968,13 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3010,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3045,13 +3045,13 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3122,13 +3122,13 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3158,7 +3158,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3199,13 +3199,13 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3235,13 +3235,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3276,13 +3276,13 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3312,7 +3312,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3353,13 +3353,13 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3430,13 +3430,13 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3507,13 +3507,13 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3543,13 +3543,13 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3581,16 +3581,16 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3617,7 +3617,7 @@
         <v>9</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3626,7 +3626,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3661,13 +3661,13 @@
         <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3738,13 +3738,13 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3774,13 +3774,13 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3815,13 +3815,13 @@
         <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
         <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3851,7 +3851,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -3892,13 +3892,13 @@
         <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
         <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>8</v>
@@ -3969,13 +3969,13 @@
         <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4046,13 +4046,13 @@
         <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4082,13 +4082,13 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4153,19 +4153,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4185,19 +4185,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4249,19 +4249,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5086,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5118,16 +5118,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920065</v>
+        <v>22330051920064</v>
       </c>
       <c r="B2" t="s">
         <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5141,22 +5141,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920065</v>
+        <v>22330051920064</v>
       </c>
       <c r="B3" t="s">
         <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5164,16 +5164,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5210,16 +5210,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920053</v>
+        <v>22330051920084</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920054</v>
+        <v>22330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5256,16 +5256,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920059</v>
+        <v>22330051920053</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5279,16 +5279,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920061</v>
+        <v>22330051920054</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5302,22 +5302,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920062</v>
+        <v>22330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920064</v>
+        <v>22330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5389,29 +5389,6 @@
         <v>62</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920079</v>
-      </c>
-      <c r="B14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -215,10 +215,10 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>NC</t>
@@ -1055,7 +1055,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1132,7 +1132,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1286,7 +1286,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1363,7 +1363,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1440,7 +1440,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1458,7 +1458,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1517,7 +1517,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1594,7 +1594,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1671,7 +1671,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1748,7 +1748,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1766,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1825,7 +1825,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1902,7 +1902,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1920,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1979,7 +1979,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2056,7 +2056,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2133,7 +2133,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2151,7 +2151,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2210,7 +2210,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2228,7 +2228,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2287,7 +2287,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2364,7 +2364,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2441,7 +2441,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2518,7 +2518,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2536,7 +2536,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2595,7 +2595,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2672,7 +2672,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2749,7 +2749,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2767,7 +2767,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2826,7 +2826,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2844,7 +2844,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2903,7 +2903,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2980,7 +2980,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2998,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -3057,7 +3057,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3075,7 +3075,7 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3134,7 +3134,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3211,7 +3211,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3288,7 +3288,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3365,7 +3365,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3442,7 +3442,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3519,7 +3519,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3596,7 +3596,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3614,7 +3614,7 @@
         <v>6</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>5</v>
@@ -3673,7 +3673,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3827,7 +3827,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3904,7 +3904,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -3981,7 +3981,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -3999,7 +3999,7 @@
         <v>6</v>
       </c>
       <c r="U42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>5</v>
@@ -4058,7 +4058,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4281,19 +4281,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -206,13 +206,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
@@ -1052,7 +1052,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1064,13 +1064,13 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -1141,10 +1141,10 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -1206,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -1218,13 +1218,13 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1283,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1295,10 +1295,10 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1360,7 +1360,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1372,10 +1372,10 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -1449,10 +1449,10 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1514,7 +1514,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1526,10 +1526,10 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1603,10 +1603,10 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1624,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1680,10 +1680,10 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1701,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1757,10 +1757,10 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1822,7 +1822,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1834,13 +1834,13 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1855,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1899,7 +1899,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -1911,13 +1911,13 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1976,7 +1976,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1988,13 +1988,13 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2006,7 +2006,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -2053,7 +2053,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2065,10 +2065,10 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2130,7 +2130,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -2142,13 +2142,13 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2163,7 +2163,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2207,7 +2207,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2219,10 +2219,10 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2284,7 +2284,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2296,10 +2296,10 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2361,7 +2361,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2373,13 +2373,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>10</v>
@@ -2438,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>7</v>
@@ -2450,10 +2450,10 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2527,13 +2527,13 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2545,10 +2545,10 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2592,7 +2592,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -2604,10 +2604,10 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2622,10 +2622,10 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2669,7 +2669,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2681,10 +2681,10 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -2758,10 +2758,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2776,7 +2776,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2823,7 +2823,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -2835,13 +2835,13 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2900,7 +2900,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2912,10 +2912,10 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2977,7 +2977,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -2989,10 +2989,10 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -3007,7 +3007,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3054,7 +3054,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>6</v>
@@ -3066,10 +3066,10 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>6</v>
@@ -3087,7 +3087,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3131,7 +3131,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>10</v>
@@ -3143,10 +3143,10 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3164,7 +3164,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3208,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3220,10 +3220,10 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3285,7 +3285,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3297,10 +3297,10 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3318,7 +3318,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3362,7 +3362,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3374,13 +3374,13 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3439,7 +3439,7 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3451,10 +3451,10 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>10</v>
@@ -3528,10 +3528,10 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3605,10 +3605,10 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>6</v>
@@ -3623,10 +3623,10 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3670,7 +3670,7 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>10</v>
@@ -3682,10 +3682,10 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3700,7 +3700,7 @@
         <v>10</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3747,7 +3747,7 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -3759,10 +3759,10 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3824,7 +3824,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3836,10 +3836,10 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3901,7 +3901,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -3913,10 +3913,10 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -3978,7 +3978,7 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>7</v>
@@ -3990,10 +3990,10 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
         <v>6</v>
@@ -4011,7 +4011,7 @@
         <v>6</v>
       </c>
       <c r="Y42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4055,7 +4055,7 @@
         <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
         <v>10</v>
@@ -4067,10 +4067,10 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>8</v>
@@ -4088,7 +4088,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4185,19 +4185,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4217,19 +4217,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4249,19 +4249,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5086,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5118,16 +5118,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920064</v>
+        <v>22330051920068</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5141,19 +5141,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920064</v>
+        <v>22330051920068</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>62</v>
@@ -5164,16 +5164,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920079</v>
+        <v>22330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920079</v>
+        <v>22330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5210,16 +5210,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5348,16 +5348,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920334</v>
+        <v>22330051920064</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5371,24 +5371,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920067</v>
+        <v>22330051920334</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920084</v>
+      </c>
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -1058,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1076,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1135,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1212,7 +1212,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1230,7 +1230,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1366,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1443,7 +1443,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1597,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1674,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1692,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1846,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1905,7 +1905,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1982,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2000,7 +2000,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2136,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2213,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2290,7 +2290,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2367,7 +2367,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2385,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2444,7 +2444,7 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2521,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2598,7 +2598,7 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2752,7 +2752,7 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2829,7 +2829,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2906,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2983,7 +2983,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3060,7 +3060,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3078,7 +3078,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3137,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3214,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3291,7 +3291,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3309,7 +3309,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3368,7 +3368,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3445,7 +3445,7 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3522,7 +3522,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3599,7 +3599,7 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3617,7 +3617,7 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3676,7 +3676,7 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3694,7 +3694,7 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3753,7 +3753,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3830,7 +3830,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3907,7 +3907,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3925,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -3984,7 +3984,7 @@
         <v>7</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4061,7 +4061,7 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4079,7 +4079,7 @@
         <v>10</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4165,7 +4165,7 @@
         <v>35</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5210,16 +5210,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920054</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920079</v>
+        <v>22330051920059</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5256,16 +5256,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920053</v>
+        <v>22330051920061</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5279,16 +5279,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920054</v>
+        <v>22330051920064</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5302,16 +5302,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920059</v>
+        <v>22330051920316</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920061</v>
+        <v>22330051920334</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5348,16 +5348,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920064</v>
+        <v>22330051920072</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5371,22 +5371,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920334</v>
+        <v>22330051920079</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>

--- a/grupos/1CM - Estadisticos 20221.xlsx
+++ b/grupos/1CM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="171">
   <si>
     <t>Materia</t>
   </si>
@@ -1061,7 +1061,7 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -1079,7 +1079,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1138,7 +1138,7 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1215,7 +1215,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>6</v>
@@ -1292,7 +1292,7 @@
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1523,7 +1523,7 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -1600,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1754,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1772,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1831,7 +1831,7 @@
         <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -1849,7 +1849,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1908,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1926,7 +1926,7 @@
         <v>5</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -2062,7 +2062,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2080,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2139,7 +2139,7 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2157,7 +2157,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2216,7 +2216,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -2293,7 +2293,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2311,7 +2311,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2447,7 +2447,7 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2542,7 +2542,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2601,7 +2601,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>8</v>
@@ -2678,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -2696,7 +2696,7 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2755,7 +2755,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -2832,7 +2832,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>5</v>
@@ -2850,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2909,7 +2909,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>8</v>
@@ -2927,7 +2927,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2986,7 +2986,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>7</v>
@@ -3004,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3063,7 +3063,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -3081,7 +3081,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3140,7 +3140,7 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -3294,7 +3294,7 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3371,7 +3371,7 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -3389,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3448,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3525,7 +3525,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -3679,7 +3679,7 @@
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>10</v>
@@ -3756,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>9</v>
@@ -3833,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>8</v>
@@ -3910,7 +3910,7 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>9</v>
@@ -3987,7 +3987,7 @@
         <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -4064,7 +4064,7 @@
         <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>8</v>
@@ -4082,7 +4082,7 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4197,7 +4197,7 @@
         <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5086,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5164,16 +5164,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920071</v>
+        <v>22330051920054</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920071</v>
+        <v>22330051920059</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5210,16 +5210,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5233,16 +5233,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920059</v>
+        <v>22330051920064</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5256,16 +5256,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920061</v>
+        <v>22330051920316</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5279,16 +5279,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920064</v>
+        <v>22330051920334</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5302,16 +5302,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920316</v>
+        <v>22330051920071</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5325,16 +5325,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920334</v>
+        <v>22330051920072</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5348,22 +5348,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920072</v>
+        <v>22330051920079</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5371,47 +5371,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920079</v>
+        <v>22330051920084</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920084</v>
-      </c>
-      <c r="B14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>
